--- a/artfynd/A 11016-2023 artfynd.xlsx
+++ b/artfynd/A 11016-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11016-2023 artfynd.xlsx
+++ b/artfynd/A 11016-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113349358</v>
+        <v>119226037</v>
       </c>
       <c r="B6" t="n">
-        <v>101095</v>
+        <v>102921</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,20 +1190,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1659</v>
+        <v>221978</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ärtvicker</t>
+          <t>Bergjohannesört</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vicia pisiformis</t>
+          <t>Hypericum montanum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1213,29 +1213,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Porsnäs, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585700</v>
+        <v>585710</v>
       </c>
       <c r="R6" t="n">
-        <v>6443424</v>
+        <v>6443387</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1260,24 +1262,14 @@
           <t>Tryserum</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>E-Val-0181</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 st: 6443389, 585785 (5m). 5 st: 6443446, 585739 (5m).</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,13 +1278,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1300,130 +1293,7 @@
           <t>Stefan Kasselstrand</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>119226037</v>
-      </c>
-      <c r="B7" t="n">
-        <v>102921</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221978</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bergjohannesört</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Hypericum montanum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Porsnäs, Sm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>585710</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6443387</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Valdemarsvik</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Tryserum</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
